--- a/src/attributions/attributions_saliency_traj_83.xlsx
+++ b/src/attributions/attributions_saliency_traj_83.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,1140 +999,7968 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2.055726895378029e-07</v>
+        <v>0.07987850904464722</v>
       </c>
       <c r="B2" t="n">
-        <v>1.497821267548716e-05</v>
+        <v>0.0184054970741272</v>
       </c>
       <c r="C2" t="n">
-        <v>4.106057986064116e-06</v>
+        <v>0.04287027567625046</v>
       </c>
       <c r="D2" t="n">
-        <v>1.292544766329229e-05</v>
+        <v>0.1609149426221848</v>
       </c>
       <c r="E2" t="n">
-        <v>1.482538436903269e-06</v>
+        <v>0.2058341950178146</v>
       </c>
       <c r="F2" t="n">
-        <v>6.429087079595774e-06</v>
+        <v>0.09390303492546082</v>
       </c>
       <c r="G2" t="n">
-        <v>3.886815648002084e-06</v>
+        <v>0.03103094920516014</v>
       </c>
       <c r="H2" t="n">
-        <v>2.06332833840861e-06</v>
+        <v>0.07688064128160477</v>
       </c>
       <c r="I2" t="n">
-        <v>1.391168439113244e-06</v>
+        <v>0.03008916229009628</v>
       </c>
       <c r="J2" t="n">
-        <v>4.585446731653064e-06</v>
+        <v>0.04637362435460091</v>
       </c>
       <c r="K2" t="n">
-        <v>1.588222949067131e-05</v>
+        <v>0.01266849040985107</v>
       </c>
       <c r="L2" t="n">
-        <v>1.086943484551739e-06</v>
+        <v>0.03692396730184555</v>
       </c>
       <c r="M2" t="n">
-        <v>1.35740774567239e-05</v>
+        <v>0.07530964910984039</v>
       </c>
       <c r="N2" t="n">
-        <v>2.963883844131487e-06</v>
+        <v>0.2065058797597885</v>
       </c>
       <c r="O2" t="n">
-        <v>1.011899985314813e-05</v>
+        <v>0.01199582125991583</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4522209969291e-06</v>
+        <v>0.01244637090712786</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.108278401166899e-06</v>
+        <v>0.03223159536719322</v>
       </c>
       <c r="R2" t="n">
-        <v>5.808940386486938e-06</v>
+        <v>0.06439300626516342</v>
       </c>
       <c r="S2" t="n">
-        <v>2.019680778175825e-06</v>
+        <v>0.04575208202004433</v>
       </c>
       <c r="T2" t="n">
-        <v>4.225659722578712e-06</v>
+        <v>0.03936831653118134</v>
       </c>
       <c r="U2" t="n">
-        <v>2.016910002566874e-06</v>
+        <v>0.02133966982364655</v>
       </c>
       <c r="V2" t="n">
-        <v>1.375267856928986e-06</v>
+        <v>0.05189002305269241</v>
       </c>
       <c r="W2" t="n">
-        <v>4.733199602924287e-06</v>
+        <v>0.01449134387075901</v>
       </c>
       <c r="X2" t="n">
-        <v>2.736995611485327e-06</v>
+        <v>0.09226369112730026</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.725129656435456e-06</v>
+        <v>0.0507335439324379</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.91368417290505e-06</v>
+        <v>0.01831918396055698</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.892778186629585e-06</v>
+        <v>0.09717510640621185</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.151719728426542e-06</v>
+        <v>0.03381149470806122</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.561140431429521e-07</v>
+        <v>0.03334924206137657</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.609477294550743e-06</v>
+        <v>0.01897844672203064</v>
       </c>
       <c r="AE2" t="n">
-        <v>4.054021701449528e-06</v>
+        <v>0.05451633036136627</v>
       </c>
       <c r="AF2" t="n">
-        <v>5.107952802063664e-06</v>
+        <v>0.09345120936632156</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.042376763711218e-06</v>
+        <v>0.02060294151306152</v>
       </c>
       <c r="AH2" t="n">
-        <v>6.30601334705716e-07</v>
+        <v>0.04565538465976715</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.325200155923085e-07</v>
+        <v>0.03430799022316933</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.116919970125309e-06</v>
+        <v>0.05841026827692986</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.027505727004609e-06</v>
+        <v>0.03109459765255451</v>
       </c>
       <c r="AL2" t="n">
-        <v>7.169658601924311e-06</v>
+        <v>0.008888546377420425</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.164288050858886e-06</v>
+        <v>0.03358007967472076</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.84859810967464e-06</v>
+        <v>0.02261902950704098</v>
       </c>
       <c r="AO2" t="n">
-        <v>7.236487817863235e-07</v>
+        <v>0.04726584628224373</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.463952171183337e-07</v>
+        <v>0.008636167272925377</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.773708385779173e-07</v>
+        <v>0.02072134986519814</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.639219249227608e-06</v>
+        <v>0.007803372107446194</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.967619689632556e-07</v>
+        <v>0.01103625819087029</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.341798558016308e-06</v>
+        <v>0.03367894142866135</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.428516265557846e-06</v>
+        <v>0.09590371698141098</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.507138212124119e-08</v>
+        <v>0.005643880926072598</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.541603630059399e-06</v>
+        <v>0.03963362798094749</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.725677278358489e-06</v>
+        <v>0.06731299310922623</v>
       </c>
       <c r="AY2" t="n">
-        <v>6.634530222981994e-07</v>
+        <v>0.006773736793547869</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.750691914523486e-06</v>
+        <v>0.000538902822881937</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.825248887143971e-06</v>
+        <v>0.03107980638742447</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.350912932859501e-07</v>
+        <v>0.06129917502403259</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.482692250145192e-07</v>
+        <v>0.05366408079862595</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.095726111088879e-05</v>
+        <v>0.1529038846492767</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.750473529682495e-06</v>
+        <v>0.05532863363623619</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.761524673493113e-06</v>
+        <v>0.1172618195414543</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.392564740854141e-06</v>
+        <v>0.1190366372466087</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.659665127197513e-07</v>
+        <v>0.04291783273220062</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.362502075608063e-06</v>
+        <v>0.03005073219537735</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.588906095814309e-07</v>
+        <v>0.0553799532353878</v>
       </c>
       <c r="BK2" t="n">
-        <v>3.371091906956281e-06</v>
+        <v>0.04055088758468628</v>
       </c>
       <c r="BL2" t="n">
-        <v>7.316690243897028e-06</v>
+        <v>0.004756252281367779</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.752997928240802e-06</v>
+        <v>0.02264883555471897</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.844082021307258e-06</v>
+        <v>0.02906484343111515</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.099869218203821e-06</v>
+        <v>0.006697991862893105</v>
       </c>
       <c r="BP2" t="n">
-        <v>2.461940766806947e-06</v>
+        <v>0.01261751633137465</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.64128048508428e-07</v>
+        <v>0.009491250850260258</v>
       </c>
       <c r="BR2" t="n">
-        <v>5.644833436235785e-07</v>
+        <v>0.05474356189370155</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.499257678005961e-07</v>
+        <v>0.01183666102588177</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.948806811924442e-06</v>
+        <v>0.007188599556684494</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.042138698423514e-06</v>
+        <v>0.04176373779773712</v>
       </c>
       <c r="BV2" t="n">
-        <v>2.680922307263245e-06</v>
+        <v>0.04353839904069901</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.71225575893186e-07</v>
+        <v>0.04311111569404602</v>
       </c>
       <c r="BX2" t="n">
-        <v>1.621771048121445e-06</v>
+        <v>0.09689349681138992</v>
       </c>
       <c r="BY2" t="n">
-        <v>5.355992016120581e-06</v>
+        <v>0.03512294963002205</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.717900997595279e-07</v>
+        <v>0.01442744676023722</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.244430783728603e-06</v>
+        <v>0.04721651971340179</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.593310561380349e-07</v>
+        <v>0.0006516892462968826</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.03219258057652e-06</v>
+        <v>0.08194059878587723</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.208181851732661e-06</v>
+        <v>0.008962081745266914</v>
       </c>
       <c r="CE2" t="n">
-        <v>2.942622643331561e-07</v>
+        <v>0.02144186571240425</v>
       </c>
       <c r="CF2" t="n">
-        <v>6.919680686223728e-07</v>
+        <v>0.01299072429537773</v>
       </c>
       <c r="CG2" t="n">
-        <v>4.184933914075373e-06</v>
+        <v>0.05324046686291695</v>
       </c>
       <c r="CH2" t="n">
-        <v>2.557798097768682e-06</v>
+        <v>0.009578201919794083</v>
       </c>
       <c r="CI2" t="n">
-        <v>7.340219099205569e-07</v>
+        <v>0.001326556783169508</v>
       </c>
       <c r="CJ2" t="n">
-        <v>4.076101731698145e-07</v>
+        <v>0.02513404563069344</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.065903234120924e-06</v>
+        <v>0.005194230936467648</v>
       </c>
       <c r="CL2" t="n">
-        <v>3.207886152267747e-07</v>
+        <v>0.007954821921885014</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.316873178642709e-06</v>
+        <v>0.05769274011254311</v>
       </c>
       <c r="CN2" t="n">
-        <v>5.416384283307707e-07</v>
+        <v>0.02796018868684769</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.591911086507025e-06</v>
+        <v>0.05613602325320244</v>
       </c>
       <c r="CP2" t="n">
-        <v>3.936450866603991e-06</v>
+        <v>0.02280108444392681</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.326214823573537e-07</v>
+        <v>0.03858699277043343</v>
       </c>
       <c r="CR2" t="n">
-        <v>4.572078069031704e-06</v>
+        <v>0.00850977934896946</v>
       </c>
       <c r="CS2" t="n">
-        <v>6.542798018926987e-06</v>
+        <v>0.0003441181033849716</v>
       </c>
       <c r="CT2" t="n">
-        <v>6.367437435983447e-06</v>
+        <v>0.03395910933613777</v>
       </c>
       <c r="CU2" t="n">
-        <v>7.16824706614716e-06</v>
+        <v>0.008377772755920887</v>
       </c>
       <c r="CV2" t="n">
-        <v>3.154159003315726e-06</v>
+        <v>0.007651148363947868</v>
       </c>
       <c r="CW2" t="n">
-        <v>8.006355756151606e-07</v>
+        <v>0.0216364674270153</v>
       </c>
       <c r="CX2" t="n">
-        <v>6.083071752982505e-07</v>
+        <v>0.002953890711069107</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.85050646198215e-06</v>
+        <v>0.04663927108049393</v>
       </c>
       <c r="CZ2" t="n">
-        <v>9.040613804245368e-07</v>
+        <v>0.02954364009201527</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.052836180155282e-06</v>
+        <v>0.009523572400212288</v>
       </c>
       <c r="DB2" t="n">
-        <v>2.803642473736545e-07</v>
+        <v>0.01991183310747147</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.62117555646546e-06</v>
+        <v>0.01004988513886929</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.947154993966251e-07</v>
+        <v>0.01519928500056267</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.675614385021618e-06</v>
+        <v>0.01103276666253805</v>
       </c>
       <c r="DF2" t="n">
-        <v>9.748262527864426e-06</v>
+        <v>0.05370766669511795</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.142667992506176e-06</v>
+        <v>0.0241769440472126</v>
       </c>
       <c r="DH2" t="n">
-        <v>3.558825937943766e-06</v>
+        <v>0.01409948989748955</v>
       </c>
       <c r="DI2" t="n">
-        <v>2.11526116800087e-06</v>
+        <v>0.02941894717514515</v>
       </c>
       <c r="DJ2" t="n">
-        <v>6.806977125961566e-06</v>
+        <v>0.04623176530003548</v>
       </c>
       <c r="DK2" t="n">
-        <v>9.398782822245266e-06</v>
+        <v>0.04226885735988617</v>
       </c>
       <c r="DL2" t="n">
-        <v>1.382921254844405e-06</v>
+        <v>0.02020582742989063</v>
       </c>
       <c r="DM2" t="n">
-        <v>7.158431344578275e-06</v>
+        <v>0.02513639256358147</v>
       </c>
       <c r="DN2" t="n">
-        <v>3.869455667881994e-06</v>
+        <v>0.009025529958307743</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.956134721898707e-06</v>
+        <v>0.01962714828550816</v>
       </c>
       <c r="DP2" t="n">
-        <v>8.010476449271664e-06</v>
+        <v>0.02960056439042091</v>
       </c>
       <c r="DQ2" t="n">
-        <v>7.202733740996337e-06</v>
+        <v>0.07190772891044617</v>
       </c>
       <c r="DR2" t="n">
-        <v>2.680332045201794e-06</v>
+        <v>0.01518389582633972</v>
       </c>
       <c r="DS2" t="n">
-        <v>3.203614085123263e-08</v>
+        <v>0.09219600260257721</v>
       </c>
       <c r="DT2" t="n">
-        <v>9.485962664257386e-07</v>
+        <v>0.07095207273960114</v>
       </c>
       <c r="DU2" t="n">
-        <v>1.258311840501847e-06</v>
+        <v>0.0849933996796608</v>
       </c>
       <c r="DV2" t="n">
-        <v>1.467611809857772e-06</v>
+        <v>0.03447705134749413</v>
       </c>
       <c r="DW2" t="n">
-        <v>7.211657248262782e-06</v>
+        <v>0.02837145142257214</v>
       </c>
       <c r="DX2" t="n">
-        <v>2.369937874391326e-06</v>
+        <v>0.03416380286216736</v>
       </c>
       <c r="DY2" t="n">
-        <v>3.046949814233813e-06</v>
+        <v>0.006479106843471527</v>
       </c>
       <c r="DZ2" t="n">
-        <v>2.470600520609878e-06</v>
+        <v>0.0320863239467144</v>
       </c>
       <c r="EA2" t="n">
-        <v>6.382758783729514e-07</v>
+        <v>0.1309777200222015</v>
       </c>
       <c r="EB2" t="n">
-        <v>5.113337920192862e-06</v>
+        <v>0.1457803696393967</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.172140741800831e-06</v>
+        <v>0.0171047430485487</v>
       </c>
       <c r="ED2" t="n">
-        <v>2.768649665085832e-06</v>
+        <v>0.02135112695395947</v>
       </c>
       <c r="EE2" t="n">
-        <v>8.827050237414369e-07</v>
+        <v>0.002762287855148315</v>
       </c>
       <c r="EF2" t="n">
-        <v>3.141248043903033e-06</v>
+        <v>0.008769851177930832</v>
       </c>
       <c r="EG2" t="n">
-        <v>1.242074176843744e-06</v>
+        <v>0.02379268035292625</v>
       </c>
       <c r="EH2" t="n">
-        <v>7.677658118154795e-07</v>
+        <v>0.02861872501671314</v>
       </c>
       <c r="EI2" t="n">
-        <v>7.53190579416696e-06</v>
+        <v>0.06099942326545715</v>
       </c>
       <c r="EJ2" t="n">
-        <v>1.258206566490117e-06</v>
+        <v>0.0375368595123291</v>
       </c>
       <c r="EK2" t="n">
-        <v>2.33203763855272e-06</v>
+        <v>0.01000944711267948</v>
       </c>
       <c r="EL2" t="n">
-        <v>5.103941020934144e-07</v>
+        <v>0.01426123920828104</v>
       </c>
       <c r="EM2" t="n">
-        <v>2.566808689152822e-06</v>
+        <v>0.004151642788201571</v>
       </c>
       <c r="EN2" t="n">
-        <v>3.103066887888417e-07</v>
+        <v>0.002552760299295187</v>
       </c>
       <c r="EO2" t="n">
-        <v>5.607028015219839e-06</v>
+        <v>0.009713964536786079</v>
       </c>
       <c r="EP2" t="n">
-        <v>1.727313019728172e-06</v>
+        <v>0.01139052957296371</v>
       </c>
       <c r="EQ2" t="n">
-        <v>5.221010269451654e-06</v>
+        <v>0.02023380622267723</v>
       </c>
       <c r="ER2" t="n">
-        <v>7.28020722817746e-07</v>
+        <v>0.04501637816429138</v>
       </c>
       <c r="ES2" t="n">
-        <v>1.890717840069556e-06</v>
+        <v>0.06194475665688515</v>
       </c>
       <c r="ET2" t="n">
-        <v>3.022542387043359e-06</v>
+        <v>0.02075544744729996</v>
       </c>
       <c r="EU2" t="n">
-        <v>1.890856992758927e-06</v>
+        <v>0.01156019885092974</v>
       </c>
       <c r="EV2" t="n">
-        <v>2.405248324066633e-06</v>
+        <v>0.01945493742823601</v>
       </c>
       <c r="EW2" t="n">
-        <v>1.198633725607579e-07</v>
+        <v>0.0137156480923295</v>
       </c>
       <c r="EX2" t="n">
-        <v>4.151949724473525e-06</v>
+        <v>0.01309097744524479</v>
       </c>
       <c r="EY2" t="n">
-        <v>7.035915245978686e-07</v>
+        <v>0.04362381249666214</v>
       </c>
       <c r="EZ2" t="n">
-        <v>3.288046741545259e-07</v>
+        <v>0.003899507224559784</v>
       </c>
       <c r="FA2" t="n">
-        <v>3.815157469944097e-06</v>
+        <v>0.0350714810192585</v>
       </c>
       <c r="FB2" t="n">
-        <v>2.053349135167082e-06</v>
+        <v>0.03040987998247147</v>
       </c>
       <c r="FC2" t="n">
-        <v>8.906915240913804e-07</v>
+        <v>0.01558725442737341</v>
       </c>
       <c r="FD2" t="n">
-        <v>1.87288605957292e-07</v>
+        <v>0.01950979791581631</v>
       </c>
       <c r="FE2" t="n">
-        <v>6.783445769542595e-07</v>
+        <v>0.005203572101891041</v>
       </c>
       <c r="FF2" t="n">
-        <v>4.627851240002201e-07</v>
+        <v>0.01876808702945709</v>
       </c>
       <c r="FG2" t="n">
-        <v>2.171806272599497e-06</v>
+        <v>0.02986332587897778</v>
       </c>
       <c r="FH2" t="n">
-        <v>5.264115770842182e-06</v>
+        <v>0.0933331698179245</v>
       </c>
       <c r="FI2" t="n">
-        <v>8.416179184678185e-07</v>
+        <v>0.08940784633159637</v>
       </c>
       <c r="FJ2" t="n">
-        <v>3.433837264310569e-06</v>
+        <v>0.03829448670148849</v>
       </c>
       <c r="FK2" t="n">
-        <v>8.359752428077627e-07</v>
+        <v>0.06628920137882233</v>
       </c>
       <c r="FL2" t="n">
-        <v>3.58756051355158e-06</v>
+        <v>0.002568385563790798</v>
       </c>
       <c r="FM2" t="n">
-        <v>2.206753151767771e-06</v>
+        <v>0.03028249740600586</v>
       </c>
       <c r="FN2" t="n">
-        <v>4.7910327793943e-07</v>
+        <v>0.1063430607318878</v>
       </c>
       <c r="FO2" t="n">
-        <v>4.09509766541305e-07</v>
+        <v>0.05823449417948723</v>
       </c>
       <c r="FP2" t="n">
-        <v>7.852395356167108e-06</v>
+        <v>0.09240678697824478</v>
       </c>
       <c r="FQ2" t="n">
-        <v>6.926562491571531e-06</v>
+        <v>0.006317514926195145</v>
       </c>
       <c r="FR2" t="n">
-        <v>2.129381527993246e-06</v>
+        <v>0.04580127447843552</v>
       </c>
       <c r="FS2" t="n">
-        <v>9.461054446546768e-07</v>
+        <v>0.1804785281419754</v>
       </c>
       <c r="FT2" t="n">
-        <v>1.384051756758709e-06</v>
+        <v>0.01325141172856092</v>
       </c>
       <c r="FU2" t="n">
-        <v>3.563448217391851e-06</v>
+        <v>0.1066126599907875</v>
       </c>
       <c r="FV2" t="n">
-        <v>1.168573271570494e-05</v>
+        <v>0.03169495612382889</v>
       </c>
       <c r="FW2" t="n">
-        <v>5.980455171084031e-06</v>
+        <v>0.08994658291339874</v>
       </c>
       <c r="FX2" t="n">
-        <v>3.567659405234735e-06</v>
+        <v>0.0290692076086998</v>
       </c>
       <c r="FY2" t="n">
-        <v>9.152076017926447e-06</v>
+        <v>0.02274571172893047</v>
       </c>
       <c r="FZ2" t="n">
-        <v>2.913708840424079e-06</v>
+        <v>0.03691134601831436</v>
       </c>
       <c r="GA2" t="n">
-        <v>8.948064532887656e-06</v>
+        <v>0.008136369287967682</v>
       </c>
       <c r="GB2" t="n">
-        <v>5.098399924463592e-08</v>
+        <v>0.02636411786079407</v>
       </c>
       <c r="GC2" t="n">
-        <v>4.873204488831107e-06</v>
+        <v>0.04909123852849007</v>
       </c>
       <c r="GD2" t="n">
-        <v>5.256324129732093e-06</v>
+        <v>0.04885029047727585</v>
       </c>
       <c r="GE2" t="n">
-        <v>2.533623955969233e-06</v>
+        <v>0.0588897243142128</v>
       </c>
       <c r="GF2" t="n">
-        <v>1.92257948583574e-06</v>
+        <v>0.07187654078006744</v>
       </c>
       <c r="GG2" t="n">
-        <v>2.199493110310868e-06</v>
+        <v>0.04240502789616585</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>0.002549309516325593</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.0009459862485527992</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.002008705399930477</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.001543219899758697</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.0004322520107962191</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.0006495803827419877</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.0006615032907575369</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.0003753307973966002</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.002767153084278107</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.002502590185031295</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.001864414545707405</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.002626810222864151</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.001811690279282629</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.0003087909426540136</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.001669461140409112</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.001336636603809893</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.0004150399472564459</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.001603624550625682</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.001481909537687898</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.001044466160237789</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.001688735792413354</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.0004368729423731565</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.001755876815877855</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.00114070693962276</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.0007547894492745399</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.001023844466544688</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>0.0002705127990338951</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.000951190129853785</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.002843171125277877</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>0.003461388871073723</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>0.00284686591476202</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.000773811130784452</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.0009044426260516047</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.002233649371191859</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>0.003219734877347946</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.000394130649510771</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.0001185376313515007</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.0006447827909141779</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.002274715807288885</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>0.001072012819349766</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>0.001668585231527686</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.0004110538284294307</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.0002200499293394387</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.002190434606745839</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>0.001433006604202092</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.002117488300427794</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>0.004167381674051285</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.001242133788764477</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.003363905940204859</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>0.007305345963686705</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>0.003805014537647367</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>0.0001369198434986174</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>0.0008495945949107409</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>0.0006267032003961504</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>0.003240664955228567</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>0.003317505354061723</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>0.002406192012131214</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>0.0005255931173451245</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>0.003925764933228493</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>0.002588430885225534</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>0.0001910094288177788</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>0.0007925888057798147</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>0.002601332496851683</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.0001891129359137267</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.214887743117288e-05</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>0.0009141569607891142</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>0.0005016732029616833</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>0.0008819480426609516</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>0.0009194939630106091</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>5.248002707958221e-05</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>0.0008828190620988607</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>0.0005542314029298723</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>0.0005372262094169855</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>0.003618310671299696</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>0.001473624259233475</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>9.551923722028732e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>0.002675717696547508</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>0.0002597381244413555</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>0.00180392898619175</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>0.0003816065145656466</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>0.001961553236469626</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.0008304897928610444</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>0.0003698319778777659</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>0.001315945293754339</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>0.001817934098653495</v>
       </c>
       <c r="CH3" t="n">
-        <v>0</v>
+        <v>0.00065693783108145</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>2.471172047080472e-05</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.0003833269292954355</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>5.494279321283102e-06</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>3.248784923925996e-05</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>0.001064004027284682</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>0.004754954017698765</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>0.003678202163428068</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>0.003544901963323355</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0</v>
+        <v>0.006837943103164434</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>0.0001299339346587658</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.0006132010603323579</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>0.002211958868429065</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>0.0006015542894601822</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.001038316637277603</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>0.0004046807298436761</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>0.001260422868654132</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>0.001585735590197146</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>0.001060161623172462</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>0.0007094865432009101</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>6.799495167797431e-05</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>6.566627416759729e-05</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>0.0004653002833947539</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.002319255610927939</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>0.0003591884742490947</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>0.002772084670141339</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>0.001864513964392245</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>0.003546894527971745</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>0.002155489753931761</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.002428159583359957</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>0.003549805609509349</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>4.153582995058969e-05</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.001470723422244191</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>0.0003410605422686785</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>0.0004773635591845959</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>0.002169941086322069</v>
       </c>
       <c r="DR3" t="n">
-        <v>0</v>
+        <v>0.001189326401799917</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>9.395123925060034e-06</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.0004155781352892518</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>0.001763699692673981</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>0.0006820037378929555</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.0008652724791318178</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>0.001786205917596817</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>0.0004642848507501185</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>0.0009762353147380054</v>
       </c>
       <c r="EA3" t="n">
-        <v>0</v>
+        <v>0.001410188153386116</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>0.0001921809744089842</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.003280395641922951</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>0.0004974361509084702</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>0.0004887324175797403</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.001699400600045919</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>0.0006171597051434219</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>0.0007018772303126752</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>0.001511081587523222</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>0.001687077805399895</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>0.001454684417694807</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.001728366245515645</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>0.0002123989397659898</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>0.0009949915111064911</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.0003740631509572268</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>1.271804649149999e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>0.0008557204273529351</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>0.0004446235252544284</v>
       </c>
       <c r="ES3" t="n">
-        <v>0</v>
+        <v>0.001580134616233408</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>0.002358167665079236</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>6.207521073520184e-05</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>7.536448538303375e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>0.0005801510997116566</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.001006819540634751</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>0.0001496383338235319</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>0.001213294453918934</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>0.001183661515824497</v>
       </c>
       <c r="FB3" t="n">
-        <v>0</v>
+        <v>0.001763656153343618</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>0.0004003939975518733</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.0001252812508028001</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>0.0001139544765464962</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>6.530893733724952e-05</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.001086594304069877</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>0.001777706784196198</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>0.001383790746331215</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>0.0004551497404463589</v>
       </c>
       <c r="FK3" t="n">
-        <v>0</v>
+        <v>0.002053734846413136</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>0.0001632489147596061</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>0.002396078314632177</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>0.001603051903657615</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>0.001651645172387362</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.002695335540920496</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>0.0001182312844321132</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>0.001967324176803231</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>0.002689169254153967</v>
       </c>
       <c r="FT3" t="n">
-        <v>0</v>
+        <v>0.001735491561703384</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>0.003138486295938492</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.001393736572936177</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>0.00820537842810154</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>1.609159517101943e-05</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.0008498150273226202</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>0.00114652793854475</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>0.001785468775779009</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>0.001370391342788935</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>0.001087482087314129</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>0.000384757062420249</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>1.478959165979177e-05</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>0.001778787700459361</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>0.0005438296357169747</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.08882430195808411</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6512104272842407</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1561812460422516</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.08549537509679794</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1709708720445633</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3178238868713379</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1089110746979713</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.00791630893945694</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0006947293877601624</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.06562799960374832</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.7896462678909302</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2241598069667816</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1261201202869415</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2973342537879944</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.3014509081840515</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.08844944834709167</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.168995589017868</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1180611103773117</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.03757259249687195</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.06293537467718124</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.0008723614737391472</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1951485127210617</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1196962893009186</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1292649656534195</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.02007971704006195</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.1192370504140854</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.1272080540657043</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.03631768003106117</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.0736382007598877</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.04289988800883293</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.08016940206289291</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.2194867432117462</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.04808177426457405</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.01372142881155014</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1952877789735794</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.008548161014914513</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.0443156473338604</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1461921632289886</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.08447456359863281</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.02158225513994694</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.1879637539386749</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.01761917024850845</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.05503204837441444</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.001071764738298953</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.1361743062734604</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.03498686105012894</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.5677707195281982</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.0561155378818512</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.02894213423132896</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.1271723657846451</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.08308503776788712</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.06576872617006302</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.1635271906852722</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.1458046138286591</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.00193985179066658</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.1179962009191513</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.1000115424394608</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.02467562630772591</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.01700794138014317</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.08029568195343018</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.2134958207607269</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.06212540715932846</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.1217060163617134</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.0364035852253437</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.001870714128017426</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0.01391837373375893</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.1176393330097198</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.003379836911335588</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.01496326737105846</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.2295858561992645</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.03402207046747208</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0.006602484732866287</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0.008765460923314095</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.352662205696106</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0.09466429799795151</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0.03694199025630951</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.05942297354340553</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.2099187672138214</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.02462755888700485</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0.02863551676273346</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.108627088367939</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.0151756014674902</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.2213965803384781</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.03135337308049202</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.009287617169320583</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.01052889227867126</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.1204996109008789</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.04893071949481964</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.001953694969415665</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0.02613193355500698</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0.1264245957136154</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0.2335289716720581</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0.1219136714935303</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0.04256053268909454</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.03049134090542793</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.01023054681718349</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0.04779770970344543</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0.05844618007540703</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0.008983846753835678</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0.03653737157583237</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>0.2228019833564758</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0.03590487688779831</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0.01690812036395073</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>0.0255657322704792</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.1368348598480225</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0.05304931476712227</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0.004109869245439768</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0.001303967088460922</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0.08001277595758438</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0.01522333174943924</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0.02007182687520981</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0.02243196964263916</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.1062776893377304</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0.03809307515621185</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0.001398483291268349</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.04136282950639725</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>0.04647498205304146</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0.07548080384731293</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>0.138668105006218</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>0.009977048262953758</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>0.04196294397115707</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>0.01057761721313</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.07513654977083206</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0.02601884305477142</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0.1018475145101547</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>0.06133005023002625</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0.02763631381094456</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>0.08480776101350784</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0.02880572527647018</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0.07622873038053513</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>0.09789501130580902</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.1806332916021347</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>0.0346573069691658</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>0.150325819849968</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>0.01593028381466866</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0.008722652681171894</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>0.1460427939891815</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>0.007916750386357307</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>0.2786040008068085</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>0.01852760836482048</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>0.09266579896211624</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>0.005356075707823038</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>0.04412927851080894</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>0.04246615245938301</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>0.03465228527784348</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>0.1197706535458565</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>0.02447407692670822</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0.09412110596895218</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>0.1120038479566574</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.0434085838496685</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>0.07161382585763931</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>0.08449411392211914</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>0.02777087315917015</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>0.03160893172025681</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>0.2417408972978592</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>0.02737249061465263</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>0.004245137795805931</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>0.009987869299948215</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>0.1246114894747734</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>0.05526106804609299</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0.03064770251512527</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>0.01289726234972477</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>0.0032306257635355</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>0.08768400549888611</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0.002055395394563675</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>0.05102390795946121</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>0.05385854840278625</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.05664875358343124</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>0.06138605996966362</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>0.170959934592247</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0.1294731944799423</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>0.07108989357948303</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.1903605610132217</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0.01199506968259811</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>0.1667858958244324</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.04349076002836227</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0.2758956253528595</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>0.2669922709465027</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0.05741298943758011</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>0.07911980152130127</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0.001384945586323738</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>0.1002173572778702</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0.01886852085590363</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0.02072132937610149</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>0.01283549051731825</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0.08683434128761292</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>0.09536568820476532</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0.01054473500698805</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>0.02262743189930916</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.01325380243360996</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.006944804452359676</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.02811879105865955</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.02937283739447594</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.003963414113968611</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.003633362706750631</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.01453434955328703</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.009091567248106003</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.003243322251364589</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.006036275997757912</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.02496453560888767</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.009931606240570545</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.03684709966182709</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.017957529053092</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.02671312540769577</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.002386203268542886</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.0003288129228167236</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.003744645044207573</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.004102621227502823</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.004201797768473625</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.01366727147251368</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.001215354539453983</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.008193922229111195</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.007721042260527611</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.006200382485985756</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.00907523836940527</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.005518411286175251</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.002401846228167415</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.00525708356872201</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.002449393272399902</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.008716796524822712</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.003629543352872133</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.000827611074782908</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.005736416671425104</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.009381996467709541</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.002240555128082633</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.01325994543731213</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.005780283361673355</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.004376346245408058</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.0007828264497220516</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.002060024999082088</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.003789495211094618</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.003355973633006215</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.004120008554309607</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.007148420438170433</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.02139115519821644</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.01882642693817616</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.01291160099208355</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.00621038768440485</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.0003491323441267014</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.02397255413234234</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.00573506485670805</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.0004016844322904944</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.005458622239530087</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.0186267327517271</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.004470760468393564</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.004721064586192369</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.02542600780725479</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.02271719835698605</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0.02279195748269558</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.01432791352272034</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.01906426437199116</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.00270529929548502</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.0006589491385966539</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.007268555462360382</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0.009679108858108521</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.003302197903394699</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.004475213121622801</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.006649655289947987</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.00287114642560482</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.002578040817752481</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0.003965469542890787</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0.01032308954745531</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0.002757251262664795</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0.01261132955551147</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0.004924556706100702</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0.006756679620593786</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0.005797434598207474</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.0078639080747962</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0.001365958596579731</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.007446257397532463</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.004061250016093254</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.003074444597586989</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.01212329789996147</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.00741111021488905</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.001591952051967382</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.003404004964977503</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.001660219393670559</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.004264859016984701</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0.0004489985876716673</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0.00829963106662035</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0.01558856572955847</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0.02555037289857864</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0.007851380854845047</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.008872879669070244</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0.01335968915373087</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0.005398932378739119</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0.0240557249635458</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0.00225047511048615</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0.005603883415460587</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0.00629538344219327</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0.007940991781651974</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0.006067456211894751</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0.002789903897792101</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0.005516764242202044</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0.001883378718048334</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0.003989259712398052</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0.0007342489552684128</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0.006838489323854446</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>0.01556829828768969</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0.0007673260988667607</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0.01349134184420109</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0.008342364802956581</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0.0108683779835701</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0.02762214466929436</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.0009697092464193702</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0.001826735911890864</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0.002007091883569956</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>0.0145009309053421</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0.02027665078639984</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0.01517992001026869</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>0.02822299860417843</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0.009365775622427464</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0.007950602099299431</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0.006172146648168564</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0.0003725545248016715</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0.007459637243300676</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0.004967890214174986</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0.01724132150411606</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0.01710241846740246</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0.02088233456015587</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0.01395836286246777</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0.002039080020040274</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0.005735202692449093</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0.004607411567121744</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>0.008892711251974106</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>0.003033658023923635</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0.004042758140712976</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0.01472406834363937</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>0.002311686519533396</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0.0006186258979141712</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0.003144869580864906</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0.004436914809048176</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0.001589165767654777</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0.001331578940153122</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>0.004969603847712278</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0.007929714396595955</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0.0007692389190196991</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>0.01278900261968374</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0.01421093102544546</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0.003380198031663895</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0.009834557771682739</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0.0005068887840025127</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0.004369767382740974</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>0.004410753026604652</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0.006304258946329355</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0.007495534606277943</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>0.003784363390877843</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>0.004006467759609222</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0.000283106928691268</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0.004011704586446285</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0.0003311028121970594</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0.008115123026072979</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>0.005134063772857189</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0.009824748151004314</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0.02050788514316082</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>0.003418509382754564</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0.001691091456450522</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0.01585102826356888</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0.01400130614638329</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>0.0025209691375494</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>0.001352401217445731</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>0.03207948431372643</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0.01755152083933353</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0.02254770696163177</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>0.03704408928751945</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>0.01457178499549627</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0.005701743066310883</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0.00110233633313328</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0.00783041026443243</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0.0171920508146286</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>0.01146956719458103</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0.01685496047139168</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0.01233234815299511</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0.01142316590994596</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>0.001530004548840225</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>0.01273923367261887</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0.003713532583788037</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0.0002839221269823611</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.002495193388313055</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.00021750146697741</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.009633740410208702</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.01184667833149433</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.001367690274491906</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.001509751542471349</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.002886796602979302</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0002245851210318506</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.001573609421029687</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.001242366386577487</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0004367589426692575</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.008642407134175301</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.01257743034511805</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0009581069462001324</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.002082470338791609</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.000543228117749095</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.002974200760945678</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.002243517665192485</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.0001667740871198475</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.001255015027709305</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.001452087191864848</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.001770238275639713</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.0008115111850202084</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.004982554353773594</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.0009220243664458394</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.0001479460042901337</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.0001265080500161275</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.0004734322428703308</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.012646291404963e-06</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.002096419688314199</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.001106315990909934</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.005523159168660641</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.001092006918042898</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.001263845479115844</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.003766426350921392</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.001262207399122417</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.001026997459121048</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.0007435381994582713</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.002073440700769424</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.004138142336159945</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.001718409126624465</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.0001206776069011539</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.001480889739468694</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.0003866933984681964</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.000155737332534045</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.002172227948904037</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.001742527121677995</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.008162149228155613</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.008331735618412495</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.005352452397346497</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.004057094920426607</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.002144826808944345</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.0009565710788592696</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.003041237127035856</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.003960873000323772</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.001139794010668993</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.0001540627563372254</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.003375300206243992</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.006211829371750355</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.004117220174521208</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.001432643388397992</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2.977153053507209e-05</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.002476636786013842</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.0004539984511211514</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.001316126901656389</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.001611406332813203</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.0005914535140618682</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.002258501714095473</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.002061734441667795</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.0002531455247662961</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0.001301805721595883</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0.0001077770139090717</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.596371293999255e-05</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.0009858333505690098</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0.00390274915844202</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.005786108318716288</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.0016965102404356</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.0007281858706846833</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.0017783441580832</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0.001545267296023667</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.001670894213020802</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.00042280915658921</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.0009791571646928787</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.002355525037273765</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.002937107579782605</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.0001738251012284309</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.0005954151274636388</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.0004168032319284976</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.0001522649545222521</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0.001167356967926025</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0.0006955723511055112</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0.002258569002151489</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0.0002406913117738441</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.0008065276779234409</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.009252202697098255</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.0001218648685608059</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0.00154391466639936</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0.0007481708889827132</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0.003521125763654709</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0.0007643858552910388</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>5.364409298636019e-05</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0.002336380071938038</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0.003041514428332448</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.0003624000237323344</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.001291411928832531</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0.0003743208362720907</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0.0001260406570509076</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0.0003953508567065001</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0.0008378138300031424</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0.001796204480342567</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.006257402710616589</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0.001702207955531776</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0.00441673444584012</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.002839956432580948</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0.0007042618817649782</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.006265564355999231</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>4.037913458887488e-05</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0.001649972517043352</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>2.517122629797086e-05</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0.0001755966513883322</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0.001681266352534294</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.002535654697567225</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.0004849520919378847</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0.0005153433885425329</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0.001347496756352484</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0.00398955075070262</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0.001923017436638474</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>5.585633334703743e-05</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0.0009991065599024296</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>0.001161938766017556</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>0.0003165268281009048</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.003891194239258766</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0.001721085980534554</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0.002775120083242655</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0.001413128571584821</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0.0004749649378936738</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>0.0002029008464887738</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>0.001502397353760898</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0.002470832085236907</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>0.002098436467349529</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0.0002449401654303074</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0.0006766864680685103</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0.0007797529688104987</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0.0008630183292552829</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0.0006940783932805061</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>0.001924971700645983</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>0.0002980388817377388</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0.002920165425166488</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>0.0007108004647307098</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0.003827780717983842</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0.001601818017661572</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0.0003562782658264041</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0.002030713483691216</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0.0005051176995038986</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0.001125136623159051</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0.002161828801035881</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0.003241822356358171</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0.0006418621633201838</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.0009467647178098559</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0.0005787290283478796</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0.000871925032697618</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>0.000318988983053714</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0.0005093567306175828</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>0.0005118907429277897</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0.003397707594558597</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>0.002049054251983762</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.002717377152293921</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.002328947652131319</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0.00016519840573892</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0.0008016119245439768</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0.003660251153632998</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0.002790571423247457</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>0.00122293911408633</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0.001301666721701622</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0.00253919349052012</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>0.003949227277189493</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0.002325154608115554</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0.002060197060927749</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0.004467173013836145</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>0.002235149266198277</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0.0007302274461835623</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>0.003109014825895429</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0.00287564261816442</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>0.002798563335090876</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>0.004790718667209148</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.002191555220633745</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>0.003477128455415368</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0.0008810760919004679</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0.0006094550481066108</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.0003616031026467681</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0009679049253463745</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.638212703866884e-05</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.006410694681108e-05</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0002506359305698425</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0005552884540520608</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0004597627557814121</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0004228037723805755</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.451453034766018e-06</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0002190809173043817</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.00130059476941824</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.097009226214141e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0005391376907937229</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0004993693437427282</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0006081640021875501</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0001824490900617093</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.0002197356952819973</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.000362174236215651</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.0001044543096213602</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.0002158847491955385</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5.915750080021098e-05</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.0002913060015998781</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.289764183340594e-05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.045742389280349e-05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.0001021212156047113</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.0001212456845678389</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>6.451212539104745e-05</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>7.511454896302894e-05</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.604092125897296e-05</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.150572592858225e-05</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.0003331371117383242</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.0006218175403773785</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0003747074224520475</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.0001135467682615854</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.000767584249842912</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.0002253053680760786</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>4.970369627699256e-05</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.0001250291243195534</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>3.814513911493123e-05</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>4.584161069942638e-05</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.0001573633926454931</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>9.107768710236996e-05</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.0001655871892580763</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.0003057502617593855</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.0001058531779563054</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.0002536440442781895</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.001473678275942802</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.0001256741816177964</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.0002148122439393774</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.000631114759016782</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.000672742840833962</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>7.556501077488065e-05</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.37664197711274e-06</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.0001775096170604229</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.0001632612547837198</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.000355097814463079</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.394065111526288e-05</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.763592733070254e-05</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>4.946425906382501e-05</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0.000138426199555397</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.0001421242486685514</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.000349045149050653</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>8.778029587119818e-05</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>9.734217019286007e-05</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.0004039934428874403</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>3.651332372101024e-05</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>2.574837708380073e-06</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.0002609143266454339</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0.000166532932780683</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0.0006118656019680202</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0.0002342966326978058</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0.0003905977355316281</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>2.973238406411838e-05</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.00085335603216663</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>9.423512892681174e-06</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0.0003760936378967017</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0.0001036533431033604</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0.0001469070557504892</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0.0001930218422785401</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0.0001968722499441355</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.0001477830955991521</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>1.323085962212645e-05</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.0003148241667076945</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>4.119974255445413e-05</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.0001030052953865379</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>7.218409882625565e-05</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>9.602215141057968e-05</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0.0001182588312076405</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.0001331175299128518</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0.0001318520808126777</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0.0002641419996507466</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0.0005803948733955622</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0.0002418511139694601</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0.0002198071160819381</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0.0002159211726393551</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0.0001045518074533902</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0.0002911985502578318</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>8.018211519811302e-05</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0.0002890870673581958</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0.0001022543001454324</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0.0002911589690484107</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>5.46055962331593e-05</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>1.124928530771285e-05</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>3.581113196560182e-05</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0.0001332914835074916</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>1.919745955092367e-05</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0.0001214457442983985</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0.0001035010209307075</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0.0004385359352454543</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0.0002382523380219936</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>4.9304508138448e-05</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>5.023959965910763e-05</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0.0001933975145220757</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>3.210269278497435e-05</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0.0001114294136641547</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0.0001792957773432136</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0.0002765112731140107</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.0002819219371303916</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>8.09367120382376e-05</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>8.713697025086731e-05</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0.0004124606493860483</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>5.469840107252821e-05</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0.0002794049214571714</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0.0002182964235544205</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>9.394494554726407e-05</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0.0001310529187321663</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>9.049208892975003e-05</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0.0003572064160834998</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0.0001001417258521542</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>3.789128459175117e-05</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0.0001727287599351257</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0.0001107662392314523</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0.0002143940509995446</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0.0002483150165062398</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0.0001357534492854029</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>7.458898471668363e-05</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>9.005768515635282e-05</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>3.403562004677951e-05</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0.00011015722702723</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>0.000102249308838509</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0.0001149814197560772</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>3.403653317946009e-05</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0.0001029860432026908</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>3.83174883609172e-05</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>6.745465361746028e-05</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>8.151059591909871e-05</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>8.077638631220907e-05</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0.000106165447505191</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>0.0002969680353999138</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0.0001926073746290058</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>9.33879055082798e-05</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>4.431715933606029e-05</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>2.937998942798004e-05</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>7.39336246624589e-05</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>0.0003927592188119888</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>2.367373599554412e-05</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>1.427812094334513e-06</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>2.609837974887341e-05</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>5.899565439904109e-05</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0.0001057502668118104</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>8.718854223843664e-05</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>2.934125404863153e-05</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>4.568658187054098e-05</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>0.0002595476107671857</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0.0001412498386343941</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0.0002873342018574476</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0.0001418040774296969</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0.0003348127938807011</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0.0001408873504260555</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0.0001883032964542508</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0.0004443245707079768</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0.0001789675152394921</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0.0002828552387654781</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0.000175956534803845</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0.0001939811045303941</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>0.0006218521157279611</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>8.39586864458397e-05</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>5.643109034281224e-06</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0.0006061269668862224</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>2.460717223584652e-05</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>1.45681005960796e-05</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>3.313272827654146e-06</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0.0001345072960248217</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0.0001211174894706346</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0.0003340659895911813</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0.0003172257565893233</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>6.575891165994108e-05</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0.0001458399783587083</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>7.751373050268739e-05</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.000432603235822171</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.007521543186157942</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.001572341192513704</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.004592028446495533</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.001607378595508635</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0006848064949735999</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.002041413215920329</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.00121798668988049</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.045123205287382e-06</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0007703218143433332</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.008031527511775494</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002099734032526612</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.006257165223360062</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002457474591210485</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0004119652148801833</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.001483866479247808</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.001087432960048318</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.0002778465859591961</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.000114154361654073</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.0007132141618058085</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.0007539768703281879</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.0005377110792323947</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.00125991040840745</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.00102146586868912</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.0003490507660899311</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.000752402120269835</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.001568499719724059</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.0008234825218096375</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.0001156034122686833</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.000278967636404559</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.0009976334404200315</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.0002469793253112584</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.001714795478619635</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.0006123605417087674</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.000539975764695555</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>8.726220403332263e-05</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>7.566704880446196e-05</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.001287409104406834</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.0003838511765934527</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.001788466004654765</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.000418836047174409</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.0009838159894570708</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.0004105177940800786</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.0003066555655095726</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.0001695984974503517</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.00023149952176027</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.005284077022224665</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.000675621151458472</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.001929038087837398</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.00264977547340095</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.000355294207111001</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.0002912439231295139</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.0008583509479649365</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.0004379419842734933</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.696428029797971e-05</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.0001188914466183633</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.001077211927622557</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.0009797773091122508</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.0001950681034941226</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.0007748564821667969</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.0006064411136321723</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.001608586288057268</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.000668778782710433</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.0001846504746936262</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.0001625458535272628</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.0009779415559023619</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.0009991396218538284</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.001425315043888986</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>9.731340105645359e-05</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.0002936855307780206</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.0006521040922962129</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>7.269459456438199e-05</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.0005236831493675709</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.003520731814205647</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.0001874892186606303</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.001498286845162511</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.0008796585607342422</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.001276054419577122</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.0008101292769424617</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.0001661314163357019</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.001205265172757208</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.0001227725006174296</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.002003484172746539</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.0007140422239899635</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.001881804782897234</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>2.613622928038239e-05</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.0002253276616102085</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>4.895668826065958e-05</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>1.131265889853239e-05</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.0003288868756499141</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.0007511213188990951</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.002673940034583211</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.0005939275724813342</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.003342431969940662</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>4.679113044403493e-05</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.00128321279771626</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.0004409487009979784</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.0006082156323827803</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.0009271826129406691</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0.000105715065728873</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0.001956927124410868</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0.000562320405151695</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.001814770279452205</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.0003653698659036309</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.0001949282013811171</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>3.51801973010879e-05</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>1.502345912740566e-05</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0.0005329899140633643</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.0004234765947330743</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.002426418708637357</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0.0001752072421368212</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.001363384071737528</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.001569956890307367</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.002336144680157304</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.0001718154671834782</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.001943754614330828</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0.001179768471047282</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.0001075157560990192</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.001308255828917027</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.001205821754410863</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.0007825700449757278</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.000780705944634974</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.0008172590751200914</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.0005639355513267219</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.001103820628486574</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0.002204282442107797</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.0002137465344276279</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.0005681533366441727</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0.0004584169946610928</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.001096653169952333</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.0004465787496883422</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.001053188578225672</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0.0003207687987014651</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.003102062502875924</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0.001789839239791036</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0.0001184860593639314</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.002391330897808075</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>6.703782128170133e-05</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.0018209433183074</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.0004725411999970675</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>4.208993777865544e-05</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0.0001944912655744702</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>4.72112515126355e-05</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0.0004576955980155617</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0.0002062412822851911</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0.001208180328831077</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0.0001342735922662541</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0.0008519096882082522</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0.000367196393199265</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>1.792883267626166e-06</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0.0008284503128379583</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0.0003169428091496229</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0.001004188670776784</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0.0001289218926103786</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>0.002413637237623334</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>0.0005632694810628891</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.002138729440048337</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>0.0001671586651355028</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.0005691236583516002</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0.0001043821539497003</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0.0001577064103912562</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>0.000521009904332459</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0.0004318223800510168</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>0.001292717293836176</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0.0007963023381307721</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.0008333175210282207</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0.0001969288132386282</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.0005926338490098715</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>6.383158324752003e-05</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0.001009175204671919</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0.000976092997007072</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0.001057231798768044</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.000513973121996969</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0.0004555775667540729</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.001293153967708349</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.001106047537177801</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.0005766914109699428</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0.0001853163121268153</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0.0004639761173166335</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0.002095486503094435</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0.001025748089887202</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>0.001937682507559657</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0.0002173037501052022</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0.0008454733761027455</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0.00352437817491591</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0.0004267700714990497</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0.001709597418084741</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>9.699098882265389e-05</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0.0001772478863131255</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1.455199799238471e-05</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4.41787597083021e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8.338643965544179e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7.16640579412342e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.728764780447818e-07</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.664212686591782e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.015564859902952e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.670998350775335e-06</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.531580998445861e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.041607356455643e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.599847984034568e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.429606739606243e-06</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.619714021217078e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>9.76873798208544e-06</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.704372698441148e-05</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.766056084306911e-05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.414605478406884e-05</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7.709366400376894e-06</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.186899109801743e-06</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5.213452823227271e-06</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.003384568321053e-06</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.203313331643585e-05</v>
+      </c>
+      <c r="W10" t="n">
+        <v>6.280853995122015e-06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.037617721522111e-06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.451402674021665e-06</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.458176029700553e-05</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.155120000679744e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>6.996417596383253e-06</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.105618816334754e-06</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.498620688129449e-07</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>9.218369086738676e-06</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.452561238897033e-05</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4.587039938996895e-07</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.887646249087993e-06</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.759557562763803e-05</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.086712472897489e-06</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>4.284429451217875e-06</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>7.184041805885499e-07</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>3.828316039289348e-06</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.050762512022629e-05</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2.839541139110224e-06</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>7.26201392353687e-08</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.051435629051412e-05</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.543365942779928e-05</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.452611286367755e-06</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.287279337702785e-05</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.072568819741718e-05</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.357207222303259e-06</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.093692379887216e-06</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>2.146861879737116e-05</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.07434007077245e-05</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>7.726810054009547e-07</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.092706588678993e-05</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3.954633029934485e-06</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.166144208284095e-06</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.091709120577434e-06</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>2.98079612548463e-07</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>7.079599981807405e-06</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.76853563466284e-06</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1.400465862388955e-06</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>7.057746643113205e-06</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.018909097183496e-05</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6.597060746571515e-07</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>5.429391876532463e-06</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.12676762000774e-05</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>2.066120714516728e-06</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>2.537261025281623e-06</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>5.633851742459228e-06</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>2.885184358092374e-06</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1.749166403897107e-05</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>3.839015334961005e-06</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>3.587749688449549e-06</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>2.604382871140842e-06</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>2.977431540784892e-05</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>3.100004960288061e-06</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1.153746688942192e-05</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.556043116579531e-06</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>5.309495008987142e-06</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>7.039585852908203e-06</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>7.220710358524229e-07</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>2.184835238949745e-06</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>1.427158622391289e-06</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>1.301913107454311e-05</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>6.482824232989515e-07</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>1.308381570197525e-06</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>1.768138872648706e-06</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>6.090560873417417e-06</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>2.351794591959333e-06</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>9.143889201368438e-07</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>9.693387710285606e-07</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>6.700145604554564e-06</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>3.261041274527088e-05</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>8.108690053632017e-06</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>1.408921707479749e-05</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>1.070342204911867e-05</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>2.454063178447541e-06</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>3.947820914618205e-08</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>5.606671038549393e-07</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>2.724701744227787e-07</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>3.365448719705455e-07</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>1.366881406283937e-05</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>7.880190651121666e-07</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>2.888946937673609e-06</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>1.697378934295557e-06</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>5.816214525111718e-06</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>1.147590182881686e-07</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>3.047916834475473e-07</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>1.46472279993759e-06</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>3.378144128873828e-06</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>1.600700329618121e-06</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>3.660178663267288e-06</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>1.311519918090198e-05</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>2.177927308366634e-05</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>3.997248313680757e-06</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>4.212438398099039e-08</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>8.529901606380008e-06</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>9.660934665589593e-07</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>3.89453407478868e-06</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>1.460064413549844e-05</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>3.591028189475765e-06</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>1.114555288950214e-05</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>9.660057912697084e-06</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>2.509375462977914e-06</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>1.380186290589336e-06</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>1.261867782886839e-05</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>2.110294644808164e-06</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>1.059652458934579e-05</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>4.302705747250002e-07</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>7.881478268245701e-06</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>2.155105676138191e-06</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>1.181776769954013e-05</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>1.03630691228318e-05</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>4.505891865846934e-06</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>3.076759639952797e-06</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>8.921326298150234e-06</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>2.320594603588688e-06</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>3.088017365371343e-06</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>3.96951236325549e-08</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>1.922889396155369e-06</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>5.054262146586552e-06</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>2.854371132343658e-06</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>1.594751211086987e-07</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>2.755422656264273e-06</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>1.034601041283167e-06</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>1.667473497946048e-06</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>9.266749430025811e-07</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>2.608542899906752e-06</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>2.028188191616209e-06</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>6.273011422308628e-06</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>5.655185759678716e-06</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>3.446055870881537e-06</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>5.331577540346188e-06</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>1.017784779833164e-05</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>1.082098378901719e-06</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>1.545643681311049e-05</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>5.54223788640229e-07</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>2.215706672359374e-06</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>9.404654974787263e-07</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>4.904897195956437e-06</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>3.217096718799439e-06</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>1.582019649504218e-06</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>1.856961944213253e-06</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>4.572787929646438e-06</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>1.400767450832063e-05</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>8.645571938359353e-07</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>1.36552826006664e-05</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>7.844261745049153e-06</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>3.210976728951209e-06</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>9.62102240009699e-06</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>9.050691005541012e-06</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>2.25663870878634e-06</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>4.847713171329815e-06</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>3.896934231306659e-06</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>3.659095000330126e-06</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>1.20543973025633e-05</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>1.113209691538941e-05</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>2.465046009092475e-06</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>3.133209247607738e-09</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>3.194465080014197e-06</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>8.784785677562468e-06</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>3.434073960306705e-06</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>6.726584160787752e-07</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>6.019101419951767e-06</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>4.6745199142606e-06</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>1.089917896024417e-05</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>4.244400315656094e-06</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>6.701337497361237e-06</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>2.47197112912545e-06</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>9.16866247280268e-06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5.583782331086695e-05</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.0003206093970220536</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.62802277575247e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0003206351539120078</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8.855657506501302e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0001864182850113139</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0001119075604947284</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0002096878015436232</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7.901669960119762e-06</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7.326723334699636e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0003756057994905859</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.129051325842738e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0004379253077786416</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0001972027821466327</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0002103978185914457</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5.41619083378464e-05</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.727760824607685e-06</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5.949339538346976e-05</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5.170457370695658e-05</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5.460321517603006e-06</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6.605556336580776e-06</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.9688351029763e-05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>9.444760507903993e-05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>9.11034076125361e-05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.085628850385547e-05</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6.974535790504888e-05</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.509842306608334e-05</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.909923907485791e-05</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.540040441090241e-06</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.478808892192319e-05</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>4.325752888689749e-05</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>8.042682020459324e-05</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.0001318956929026172</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.029665327223483e-05</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.0001797786972019821</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>3.829950946965255e-05</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>3.001293043780606e-05</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3.247681161155924e-05</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>3.58501129085198e-05</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>7.305834151338786e-05</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>5.029210296925157e-05</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.229649003827944e-05</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>3.337146699777804e-05</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.042757791467011e-05</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.052755487762624e-05</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.045463123882655e-06</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.000313891563564539</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>4.668210749514401e-05</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.0001054259701049887</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.0002291570563102141</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.000133196052047424</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3.761168500204803e-06</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.990091838408262e-05</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.079674257198349e-05</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3.183083663316211e-07</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>9.851107279246207e-06</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.797937435796484e-05</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>8.853687177179381e-05</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.0001258501288248226</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>4.049398557981476e-05</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.837812305893749e-06</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.0002157608396373689</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.329841325059533e-06</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>9.23184234125074e-06</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.0001160373649327084</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1.480204446124844e-05</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>8.736663585295901e-05</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.0001301631855312735</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>3.667508281068876e-05</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>5.920428884564899e-05</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>7.432874554069713e-05</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>3.162155917380005e-05</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>4.279594941181131e-05</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.0001639014226384461</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>2.75013517239131e-05</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0.0001360083115287125</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>8.169656939571723e-05</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.0001372456317767501</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>6.121199112385511e-05</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>1.35928003146546e-05</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>3.742948319995776e-05</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>2.081378625007346e-05</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>8.557354158256203e-05</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>1.650702870392706e-05</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>9.432328806724399e-05</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>2.125695027643815e-05</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>3.485073466436006e-05</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>7.012845344434027e-07</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>3.651131191872992e-05</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>1.129824340750929e-06</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>4.486164471018128e-05</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.0001277892733924091</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.0001198713143821806</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.0001517154014436528</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>3.354477303219028e-05</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>6.116596341598779e-05</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>3.99453128920868e-05</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>7.741440640529618e-05</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>2.237961962237023e-05</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>9.223844017469673e-07</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>8.363717643078417e-05</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>2.378513454459608e-05</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.0001186337249237113</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>3.011482476722449e-05</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>3.077053042943589e-05</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>5.245562078926014e-06</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>3.515372372930869e-05</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>1.320689079875592e-06</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>6.221997318789363e-05</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0.0001255610841326416</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>2.420675446046516e-05</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.000153976128785871</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>5.787041300209239e-05</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>5.735170998377725e-05</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>8.885093848221004e-06</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.000190941515029408</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>7.321124576264992e-05</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>1.998856168938801e-05</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>4.908830305794254e-05</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>2.511071943445131e-05</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>1.041225186781958e-05</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>2.52429117608699e-06</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>7.863985956646502e-05</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>5.74270889046602e-05</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>9.584776125848293e-05</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>8.551077917218208e-05</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>2.333683369215578e-05</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>3.515517892083153e-05</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>3.621665018727072e-05</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>4.265076131559908e-05</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>4.701576835941523e-05</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>2.09008612728212e-05</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>3.991997436969541e-05</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0.0001724700559861958</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0.0001269198110094294</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>7.060417374304961e-06</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>2.373650931986049e-05</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>1.746565976645797e-05</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>8.07224860182032e-05</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>4.481275027501397e-05</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>2.884919013013132e-05</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>1.070102098310599e-05</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>1.901697214634623e-05</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>4.689297566073947e-05</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>1.306617559748702e-05</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>4.582343535730615e-05</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>3.80141063942574e-05</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>8.194614201784134e-05</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>8.438239456154406e-05</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>3.729855961864814e-06</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>4.020429332740605e-05</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>3.425590693950653e-05</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>7.553219620604068e-05</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>7.522375199187081e-06</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.0001027906182571314</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>1.539841832709499e-05</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.000130866130348295</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>7.338757313846145e-06</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>4.347668073023669e-05</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>1.279329626413528e-05</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>3.949151141569018e-05</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>1.776462158886716e-05</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>3.680116378745879e-06</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>5.565781611949205e-05</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>3.473465039860457e-05</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.0001245987805305049</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>5.0073071179213e-05</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>5.906833393964916e-06</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>3.721601387951523e-05</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>1.67822654475458e-05</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>8.407414134126157e-05</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>4.676448588725179e-05</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>4.189246465102769e-05</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>8.867997530614957e-05</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>2.404339284112211e-05</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.0001318669237662107</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>5.320058698998764e-05</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>4.590544267557561e-05</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0.0001171059338958003</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>2.237339140265249e-05</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>2.545419374655467e-05</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>4.704200364358258e-06</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>8.332915604114532e-05</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>6.278017826844007e-05</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>3.383480725460686e-05</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.0001167301306850277</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>7.906430255388841e-05</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>5.523571599042043e-05</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>1.877984686871059e-06</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.08617317676544189</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2163858562707901</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.01442702766507864</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.01806204207241535</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.138221800327301</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1666323840618134</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.01641214825212955</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.02456834726035595</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.05779736861586571</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.0727774053812027</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.3341317474842072</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.03333764895796776</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.07183429598808289</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1313359141349792</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.1885213702917099</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.09237390011548996</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1584853231906891</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.0863184928894043</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.01047239545732737</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.0378025509417057</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.004703039769083261</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.08630461990833282</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.04908134415745735</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.002379575744271278</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.01321400236338377</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.06135371327400208</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.03399282693862915</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.07677745819091797</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.01391046028584242</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.01406734623014927</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.01718560606241226</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.1927810609340668</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.07089054584503174</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.008617524057626724</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.07456368952989578</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.02893635630607605</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.005227739922702312</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.01133608445525169</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.01511805411428213</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.06184414774179459</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.02082511410117149</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.08690754324197769</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.04332037642598152</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.1263110339641571</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.01273277774453163</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.04083250463008881</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.2922334372997284</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.02993631921708584</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.04478999972343445</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.006562143564224243</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.1110424473881721</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.007004301995038986</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.02450916171073914</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.02529975213110447</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.002737326547503471</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.02495808899402618</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.007905365899205208</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.03410591185092926</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.0458233654499054</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0.07173310220241547</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0.0260799303650856</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.04519760608673096</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.003558429889380932</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.01632584817707539</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.1123146787285805</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0.04172640666365623</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.02507918514311314</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.08111263066530228</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.01136756874620914</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0.06958042085170746</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0.01278724148869514</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0.007175065577030182</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0.001365285366773605</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.1666823476552963</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0.02558504417538643</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0.02181849256157875</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0.03074382990598679</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0.07521037757396698</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0.04245860874652863</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0.02076464891433716</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.04301105812191963</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0.02291635610163212</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.06624438613653183</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.004700331017374992</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.007568102795630693</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.02266531437635422</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.0533512756228447</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.01709250174462795</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.006535992491990328</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0.02158304490149021</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0.06664940714836121</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0.1590780168771744</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0.00106333417352289</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0.07275670021772385</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.005288898944854736</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.1209529042243958</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>0.04845894128084183</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>0.03274752572178841</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>0.04724803194403648</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>0.007973795756697655</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>0.07074481248855591</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0.01210104394704103</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0.02638732641935349</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0.04228599369525909</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.04588233679533005</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0.002254194347187877</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0.007586716674268246</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0.02990198507905006</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0.006528457626700401</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.04483980685472488</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0.03863737359642982</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0.0878864973783493</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.0780196413397789</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.02822069078683853</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0.03553070873022079</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0.02839828841388226</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0.03705749660730362</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0.05443442612886429</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>0.04261475801467896</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>0.03383469954133034</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0.06515830755233765</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>0.02723026089370251</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.03756830096244812</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0.03138944879174232</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0.0120362751185894</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0.0168025828897953</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>0.06003697216510773</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>0.02554249204695225</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>0.02133307792246342</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>0.01756391860544682</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.03431076556444168</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>0.002777013927698135</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0.00119576882570982</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0.01050611957907677</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>0.1405227035284042</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>0.02185690402984619</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>0.00507352314889431</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>0.01783930324018002</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>0.01494976878166199</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>0.07445800304412842</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.004594979807734489</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>0.0006806640885770321</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>0.03999705985188484</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>0.03836169838905334</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0.0003790678456425667</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.005946699529886246</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>0.0005146705079823732</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>0.0118987588211894</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>0.08252832293510437</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>0.05402130261063576</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0.03932032361626625</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0.03186457604169846</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>0.001126231625676155</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0.0156733300536871</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>0.07621432840824127</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>0.003785450477153063</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>0.008717433549463749</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>0.05391813814640045</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.05289052799344063</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0.02505319379270077</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0.002548342105001211</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>0.03345834836363792</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>0.02930028736591339</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>0.07436396926641464</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0.0045604407787323</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>0.06084227561950684</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>0.04268116503953934</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.05194798484444618</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>0.03522561118006706</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0.096084363758564</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0.07344093173742294</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>0.001386291813105345</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>0.01237694453448057</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>0.0148558346554637</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>0.1939905434846878</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>0.06271220743656158</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>0.01446067169308662</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>0.06851420551538467</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0.09704121947288513</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0.04006193205714226</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0.04290743172168732</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>0.02458993718028069</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0.03543644025921822</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0.02673879638314247</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>0.05076883733272552</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.02994484268128872</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>0.0849360004067421</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>0.01093330513685942</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0.06950885802507401</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.3973525166511536</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.8364835381507874</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.06005102023482323</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2904163599014282</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.02072183042764664</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3669205605983734</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.19485142827034</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.02102870866656303</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3250356316566467</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.4254882037639618</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.113010883331299</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2172895967960358</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2372553944587708</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3220862448215485</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.2441603988409042</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.2671724557876587</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.06012110412120819</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.595400869846344</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.05340814217925072</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.1281475126743317</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.1597733199596405</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.0894882008433342</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.3127181529998779</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.2154370546340942</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.1155540347099304</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.1184841617941856</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.06594953685998917</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.04867275059223175</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.1527710855007172</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.154438853263855</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.1487271338701248</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.5039917826652527</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.2566698491573334</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.09848599880933762</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.104243315756321</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.02427449449896812</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.1242578700184822</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.02479448728263378</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.2241860628128052</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.1487123668193817</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.5412382483482361</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.2827828526496887</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.1366406083106995</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.1684905141592026</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.1257624626159668</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.3755225539207458</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.100111111998558</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.002891719341278076</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.123908668756485</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.550342857837677</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.1439913213253021</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.04936674609780312</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.2774925231933594</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.1158308982849121</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.227306455373764</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.6984644532203674</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.2611805498600006</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.1509274244308472</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.7669986486434937</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.325768917798996</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.1832376718521118</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.2647592723369598</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.1003292053937912</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.02744955196976662</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.2064674347639084</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.003406722098588943</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.06969641149044037</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.4199212789535522</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.07410918176174164</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.01880170404911041</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.09433948993682861</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.05453182756900787</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.1289997547864914</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.09570685029029846</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0.05329249799251556</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.04388230293989182</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.2030250728130341</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.2647958397865295</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0.1545849740505219</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0.03433027118444443</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.2165629863739014</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.162954643368721</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.1290639787912369</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.07364494353532791</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.03824983909726143</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.04005610197782516</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.1534360647201538</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.01168308779597282</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.02739150077104568</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.0966365709900856</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.07428879290819168</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.3221406638622284</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0.2036890685558319</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.05388703197240829</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.4103589951992035</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0.4152202010154724</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0.1133097559213638</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0.1576898097991943</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0.1261713206768036</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0.1561806201934814</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.1950665414333344</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0.02898122742772102</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0.04310404881834984</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.02355406060814857</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0.1500755250453949</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0.01474117301404476</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0.05479828268289566</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0.07113661617040634</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.05669640749692917</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.05188882350921631</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0.4515417218208313</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.2650741040706635</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.342552661895752</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0.1989119946956635</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0.01211611647158861</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.089035764336586</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0.3937914967536926</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.07767114043235779</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.3566314876079559</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0.1014268696308136</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.1590431332588196</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.07369384169578552</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.1723082363605499</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.02429539896547794</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0.1369805634021759</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0.2461294531822205</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.08958672732114792</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.08292145282030106</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0.1725707501173019</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.05757322162389755</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.01696516573429108</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0.06141142547130585</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0.2306608259677887</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0.4698935151100159</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0.1890057921409607</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0.1200415790081024</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.02327204681932926</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0.06704003363847733</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0.09137672930955887</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.05887977778911591</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.2396855801343918</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0.04091520607471466</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0.0551295317709446</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0.1456517428159714</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0.07783603668212891</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.01303541287779808</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0.2587224543094635</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.09719642251729965</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.02087902277708054</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0.3024249076843262</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0.1313430964946747</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0.01380573958158493</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0.1082952171564102</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0.2017534226179123</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.1813245713710785</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0.06120530888438225</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0.01301093399524689</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.0323321595788002</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0.1418626010417938</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0.007423422299325466</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0.04071324318647385</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0.1306023299694061</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0.07090985029935837</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.03825017809867859</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0.02274646237492561</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.03859866783022881</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.156337097287178</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0.06933499127626419</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0.1801812052726746</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0.1472648531198502</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0.1775691956281662</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>0.2222122550010681</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.2945221662521362</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0.2697127461433411</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.544269859790802</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.1712736040353775</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0.2248105704784393</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0.03881500661373138</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0.1213040947914124</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0.03380170091986656</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0.08124764263629913</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.03596459701657295</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0.05851172655820847</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0.1533332616090775</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>0.1255175024271011</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0.3724314570426941</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0.129801020026207</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0.1144094467163086</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0.3478595316410065</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.0006711530149914324</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.01530175842344761</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.002406422514468431</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.007962044328451157</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.003059285925701261</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.01420793496072292</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.003116157837212086</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.006931301672011614</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.001253993948921561</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.003436272498220205</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0180993340909481</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.00520985946059227</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.01383046247065067</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.009782828390598297</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.01731932908296585</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.001138250809162855</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.332186654210091e-05</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.002646191511303186</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.0003147476236335933</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.003638383466750383</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.0002890770556405187</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.00240236334502697</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.001858791103586555</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.002011269563809037</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.002730767242610455</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.003597695147618651</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.002016804646700621</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.0003832106012851</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.0005413693143054843</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.0008858788060024381</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.004282199312001467</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.006597594358026981</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.006698654033243656</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.00151656661182642</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.01353651192039251</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.0001474050804972649</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.001095902523957193</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.003736269660294056</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.0006996981101110578</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.001577944494783878</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.001300289412029088</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.0008462854311801493</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.00124187464825809</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.005906820297241211</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>3.137881867587566e-05</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.001120826578699052</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.01896310783922672</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.002489897888153791</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.004053556360304356</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.008827239274978638</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.01240616384893656</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.0003568762913346291</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.00178792851511389</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.001208745059557259</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.001803359133191407</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.001420782529748976</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.003721953369677067</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.003605079837143421</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.0001135169877670705</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0.001907816855236888</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.0008531336789019406</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.004230218473821878</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.0009604146471247077</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.001694495673291385</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.005470041185617447</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.001515242271125317</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.002974736504256725</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.0007367192883975804</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.00179902627132833</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.004025273490697145</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.001888766884803772</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.003147428389638662</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0.0007054562447592616</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.01303736120462418</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.0004203969147056341</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0.003597218543291092</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0.001528353313915431</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0.006608739960938692</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0.00368342618457973</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0.0003976470325142145</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.001247217762283981</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>2.706953091546893e-05</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.005246854387223721</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.00133448769338429</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.001751409377902746</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.001369791803881526</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.003299481933936477</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.0002669368695933372</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.001855234149843454</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0.000820825865957886</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0.002834033453837037</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0.008838481269776821</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0.00489920424297452</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0.006297447253018618</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.004164248704910278</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.0001399146858602762</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0.001279283780604601</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0.00265325722284615</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0.001960780704393983</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0.001153000281192362</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0.004763463046401739</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0.001882824813947082</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.003025884507223964</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.001435599057003856</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.004271295852959156</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0.0001055403117788956</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0.001686430536210537</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0.0002612562384456396</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.001454198034480214</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0.008458134718239307</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0.004687624052166939</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>6.182717334013432e-05</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.002054756041616201</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.008626896888017654</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0.001781281782314181</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.005959026515483856</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0.001519979210570455</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.0005023302510380745</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0.001923563191667199</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0.001541779492981732</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0.00132847554050386</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>0.0006485157064162195</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.00170318316668272</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0.002524781273677945</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0.00458376482129097</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0.001193694421090186</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0.001137282233685255</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0.001053483923897147</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0.003254522569477558</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0.0007253055227920413</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.001365630654618144</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>3.104406641796231e-05</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>0.0008438559016212821</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0.006386728957295418</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0.008593995124101639</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0.0003067119687329978</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>0.00167096545919776</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0.001043967320583761</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0.001800099737010896</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.0004800973692908883</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0.001109734061174095</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0.0002632434479892254</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0.001795542193576694</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0.0004361588507890701</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0.001389050972647965</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0.004097693599760532</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0.001268696156330407</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0.002480587922036648</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0.002863623667508364</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.001356282038614154</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0.0003462140448391438</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0.001455894205719233</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0.001229028799571097</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0.0006521613104268909</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>0.006139084696769714</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>0.0008331959834322333</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0.003147349692881107</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.0008693860145285726</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.003557003336027265</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0.0008421338279731572</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0.001387273194268346</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0.0005313450819812715</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0.000310463597998023</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.003969547804445028</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0.00212832516990602</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0.003789008827880025</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.003384686075150967</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.006863572634756565</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0.002999288029968739</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0.003545066341757774</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0.008224260993301868</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0.0001174290082417428</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.00548221031203866</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0.0016744255553931</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0.001063550589606166</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.009255273267626762</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>0.000461994088254869</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0.001062585040926933</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0.01247173640877008</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0.001951422775164247</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0.002726611914113164</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0.0008634484838694334</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0.005352770909667015</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0.001107612624764442</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>0.008435823023319244</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.005452795419842005</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>0.002997441682964563</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>6.058032158762217e-05</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0.0008737078169360757</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4.393671648728059e-09</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4.35087077477192e-09</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.456466391935862e-09</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.854796982669882e-09</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7.290536507831291e-10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.888679657113812e-09</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.124674880477073e-10</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.650709068381275e-09</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.290067691035347e-09</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.804448838768849e-09</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.623603722109237e-09</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.399453664063799e-09</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.753357903311326e-09</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9.10677311338759e-10</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.807369587325525e-09</v>
+      </c>
+      <c r="P15" t="n">
+        <v>9.838785341997891e-10</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.771617158003892e-09</v>
+      </c>
+      <c r="R15" t="n">
+        <v>5.366474487011885e-10</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.117576475806459e-09</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.281341588388329e-09</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4.686507848461474e-10</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3.609162135820299e-10</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.990103885660346e-10</v>
+      </c>
+      <c r="X15" t="n">
+        <v>9.294030822726285e-12</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4.008169907088188e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.253408792896039e-09</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.132320792684993e-09</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.431740364627899e-10</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.056460696702288e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>9.533206446477038e-10</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.199638388627022e-09</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.371655566906327e-11</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>6.29609808733278e-10</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>6.849223410654304e-10</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.698948981498916e-09</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.512856839802623e-09</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.398458986974106e-09</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>4.159504962686356e-10</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>2.631650675155583e-09</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>5.392456481345675e-10</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>4.073938408843958e-10</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.668287868961116e-10</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3.436222417718682e-10</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>8.26211543625277e-10</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.992953273053047e-10</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.309388318939455e-09</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.115370296123075e-10</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.264390481203748e-09</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>9.090908581477208e-10</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3.683734872694799e-09</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.333712195185967e-10</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.461556514177232e-10</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>3.731771280879315e-10</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.663562869211546e-10</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>7.329711282366702e-10</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>3.934930603577413e-09</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>2.287977585169187e-10</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.487358125551452e-09</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>3.095607103986708e-09</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1.5563762501003e-09</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>6.744067804209664e-11</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>2.80307688171888e-09</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>3.294454709035222e-09</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>3.417871818900409e-10</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>8.295918396683533e-10</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.878647485995202e-11</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1.868256382930866e-10</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>5.650090950659603e-10</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.120104342611228e-09</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1.114920156197741e-09</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>7.81071984867765e-10</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1.630683088560403e-10</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>2.399177079226433e-09</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>3.956301952712238e-11</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1.186495679483812e-09</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>4.012448429069337e-10</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.32128641361362e-10</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>2.111264496562626e-10</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>6.62056742761763e-10</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>1.006361438626868e-09</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>2.380000085899781e-10</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>7.039753779913838e-10</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>9.049410665262769e-10</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>3.042359697502661e-10</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>5.865856134157355e-10</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>5.096623123534982e-10</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>1.064933252692413e-09</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>4.656668939340136e-10</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>5.370285466321789e-11</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>2.421789435658184e-10</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>3.508386636763561e-11</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>1.786726544494854e-09</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>2.225877260286779e-09</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>9.015359569986003e-10</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>1.64563174198662e-09</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>1.325339393787317e-09</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>2.356781991785795e-10</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>8.785837335434366e-11</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>1.111413738819067e-09</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>4.47045400697732e-10</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>9.892344721151858e-10</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>3.594537445472668e-10</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>6.450171508021185e-10</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>5.580692019613309e-10</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>8.132020612450219e-10</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>1.625315437792096e-10</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>2.022495504405697e-10</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>6.194153523431112e-11</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>9.588652094549843e-11</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>1.30977306778135e-09</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>2.950206745566675e-09</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>6.664336860140452e-10</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>2.576365121242929e-09</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>6.544081387893641e-10</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>8.992480093894528e-10</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>1.623543632867097e-09</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>1.614899436397366e-09</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>1.228221857552114e-09</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>2.359895612258356e-09</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>1.381501135711005e-09</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>1.290118789576411e-09</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>3.818358407237099e-10</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>7.461190554280961e-10</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>6.85105638886796e-10</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>1.701112584129305e-09</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>9.378889331834728e-11</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>9.856404581398692e-10</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>9.448072324502732e-10</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>4.927653285413669e-10</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>6.822868936495752e-10</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>4.566707012543247e-09</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>7.960181402921762e-10</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>1.087055778725698e-09</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>1.217950518217492e-09</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>1.427761686656481e-09</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>7.481074093540485e-10</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>7.492921838547772e-10</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>5.369708011571106e-10</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>7.705815152636575e-11</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>1.722553488736622e-10</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>1.324939491453847e-09</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>1.462897858406365e-11</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>7.404219598550199e-11</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>4.33176827741022e-10</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>6.238702887628733e-10</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>4.907099726558783e-10</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>2.686998956669129e-10</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>1.10631115379789e-09</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>4.504448758435586e-10</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>1.116968295633569e-09</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>3.965106576409028e-10</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>1.947936256740945e-10</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>1.719325126714466e-09</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>7.094766996118551e-10</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>1.29565425055489e-09</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>1.489868367565705e-10</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>7.075857122451623e-10</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>5.094337729438791e-10</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>9.324320204839864e-10</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>3.359083011744701e-10</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>5.107299028139778e-10</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>1.433593938005018e-10</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>3.366212586453088e-10</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>1.395314752627996e-09</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>1.791294002018162e-09</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>6.114492800968208e-10</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>2.701468604371371e-09</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>4.144018184160103e-10</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>2.409731580943486e-10</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>1.598192467255899e-09</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>6.58900933814266e-10</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>1.643696179165488e-09</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>2.863253856233428e-09</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>3.492171885000062e-09</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>3.103491685862991e-09</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>5.307412842547876e-11</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>1.072426369930213e-09</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>1.568476792890294e-09</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>9.078001683704429e-10</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>3.732550102331089e-10</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>6.371332350596504e-10</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>2.111797403614446e-09</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>1.743472033410853e-09</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>3.818717841941321e-10</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>2.215566397012481e-09</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>6.188507484239381e-10</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>1.288630174789418e-10</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>4.299689077003066e-11</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>1.574536945270211e-09</v>
       </c>
     </row>
   </sheetData>
